--- a/data/wfa_best_indicator_by_sector_2024-10-21_2026-04-20.xlsx
+++ b/data/wfa_best_indicator_by_sector_2024-10-21_2026-04-20.xlsx
@@ -8,7 +8,7 @@
     <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="286be97a-f60c-4859-a8af-7c752eb" sheetId="1" state="visible" r:id="rId3"/>
+    <sheet name="bfaa6770-5c6c-493d-9f67-91c5099" sheetId="1" state="visible" r:id="rId3"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
   <extLst>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="17">
   <si>
     <t xml:space="preserve">sektor</t>
   </si>
@@ -59,6 +59,12 @@
   </si>
   <si>
     <t xml:space="preserve">Finansial</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RSI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RSI_Signal</t>
   </si>
   <si>
     <t xml:space="preserve">Industri</t>
@@ -323,19 +329,19 @@
         <v>10</v>
       </c>
       <c r="E2" s="0" t="n">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="F2" s="0" t="n">
-        <v>48</v>
+        <v>21</v>
       </c>
       <c r="G2" s="0" t="n">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="H2" s="0" t="n">
-        <v>66.6666666666667</v>
+        <v>71.4285714285714</v>
       </c>
       <c r="I2" s="0" t="n">
-        <v>70.2380952380952</v>
+        <v>76.6666666666667</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -343,10 +349,10 @@
         <v>12</v>
       </c>
       <c r="B3" s="0" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C3" s="0" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="D3" s="0" t="n">
         <v>10</v>
@@ -355,21 +361,21 @@
         <v>30</v>
       </c>
       <c r="F3" s="0" t="n">
-        <v>52</v>
+        <v>33</v>
       </c>
       <c r="G3" s="0" t="n">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="H3" s="0" t="n">
-        <v>51.9230769230769</v>
+        <v>51.5151515151515</v>
       </c>
       <c r="I3" s="0" t="n">
-        <v>61.6666666666667</v>
+        <v>57.8947368421053</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="0" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B4" s="0" t="s">
         <v>10</v>
@@ -381,24 +387,24 @@
         <v>10</v>
       </c>
       <c r="E4" s="0" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="F4" s="0" t="n">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="G4" s="0" t="n">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="H4" s="0" t="n">
-        <v>60</v>
+        <v>57.1428571428571</v>
       </c>
       <c r="I4" s="0" t="n">
-        <v>66.0714285714286</v>
+        <v>62.5</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="0" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B5" s="0" t="s">
         <v>10</v>
@@ -410,19 +416,19 @@
         <v>10</v>
       </c>
       <c r="E5" s="0" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="F5" s="0" t="n">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="G5" s="0" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="H5" s="0" t="n">
-        <v>54.1666666666667</v>
+        <v>50</v>
       </c>
       <c r="I5" s="0" t="n">
-        <v>59.2592592592593</v>
+        <v>56.6666666666667</v>
       </c>
     </row>
   </sheetData>
